--- a/tests/evals/timesheets/01-xlsx-dana-02/input.xlsx
+++ b/tests/evals/timesheets/01-xlsx-dana-02/input.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A26"/>
+  <dimension ref="A1:A25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -517,82 +517,75 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-02-16  8.00</t>
+          <t>2026-02-17  8.00</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-02-17  8.00</t>
+          <t>2026-02-18  8.00</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-02-18  8.00</t>
+          <t>2026-02-19  8.00</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-02-19  8.00</t>
+          <t>2026-02-20  8.00</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-02-20  8.00</t>
+          <t>2026-02-23  8.00</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-02-23  8.00</t>
+          <t>2026-02-24  8.00</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-02-24  8.00</t>
+          <t>2026-02-25  8.00</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-02-25  8.00</t>
+          <t>2026-02-26  8.00</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-02-26  8.00</t>
+          <t>2026-02-27  8.00</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-02-27  8.00</t>
+          <t>Total: 152.00</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
-        <is>
-          <t>Total: 160.00</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
         <is>
           <t>Approved by Sam Ortiz on 2026-02-28</t>
         </is>
